--- a/data/Bowil/investment_decision/Oberhofen_SFH_from_2015_investment_decision.xlsx
+++ b/data/Bowil/investment_decision/Oberhofen_SFH_from_2015_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,37 +460,37 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
@@ -528,7 +527,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
@@ -565,11 +564,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>21.47327895169776</v>
+        <v>17.21636965715284</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,30 +582,30 @@
         <v>3765.339905818835</v>
       </c>
       <c r="F4" t="n">
-        <v>21.01976220768333</v>
+        <v>17.3097432183429</v>
       </c>
       <c r="G4" t="n">
         <v>3765.339905818835</v>
       </c>
       <c r="H4" t="n">
-        <v>21.22022181345131</v>
+        <v>17.38771737980062</v>
       </c>
       <c r="I4" t="n">
         <v>3765.339905818835</v>
       </c>
       <c r="J4" t="n">
-        <v>21.21540437409734</v>
+        <v>17.11007699965803</v>
       </c>
       <c r="K4" t="n">
         <v>3765.339905818835</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>21.47327895169776</v>
+        <v>17.21636965715284</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,30 +619,30 @@
         <v>3765.339905818835</v>
       </c>
       <c r="F5" t="n">
-        <v>21.01976220768332</v>
+        <v>17.3097432183429</v>
       </c>
       <c r="G5" t="n">
         <v>3765.339905818835</v>
       </c>
       <c r="H5" t="n">
-        <v>21.22022181345131</v>
+        <v>17.38771737980061</v>
       </c>
       <c r="I5" t="n">
         <v>3765.339905818835</v>
       </c>
       <c r="J5" t="n">
-        <v>21.21540437409734</v>
+        <v>17.11007699965803</v>
       </c>
       <c r="K5" t="n">
         <v>3765.339905818835</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>21.96195749746112</v>
+        <v>17.41478336327435</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,26 +656,26 @@
         <v>3765.339905818835</v>
       </c>
       <c r="F6" t="n">
-        <v>21.01976220768333</v>
+        <v>17.41478336327442</v>
       </c>
       <c r="G6" t="n">
         <v>3765.339905818835</v>
       </c>
       <c r="H6" t="n">
-        <v>21.26274858039848</v>
+        <v>17.41478336327439</v>
       </c>
       <c r="I6" t="n">
         <v>3765.339905818835</v>
       </c>
       <c r="J6" t="n">
-        <v>21.26274858039848</v>
+        <v>17.41478336327438</v>
       </c>
       <c r="K6" t="n">
         <v>3765.339905818835</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -684,36 +683,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Oberhofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Oberhofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -721,36 +720,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Oberhofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Oberhofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -758,36 +757,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Oberhofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Oberhofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -795,36 +794,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Oberhofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Oberhofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -832,40 +831,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Oberhofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Oberhofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5.648009858728253</v>
+        <v>8.45381393258427</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001479428139301757</v>
+        <v>0.001013915181176471</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,30 +878,30 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001479428139301757</v>
+        <v>0.001013915181176471</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001520872771764706</v>
+        <v>0.001013915181176471</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001520872771764706</v>
+        <v>0.001013915181176471</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001479428139301757</v>
+        <v>0.001086337694117647</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,30 +915,30 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001479428139301757</v>
+        <v>0.001086337694117647</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001520872771764706</v>
+        <v>0.001086337694117647</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001520872771764706</v>
+        <v>0.001086337694117647</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001810562823529412</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,30 +952,30 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001810562823529412</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00181056282352943</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001810562823529412</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001810562823529412</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,30 +989,30 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001810562823529412</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001810562823529412</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001810562823529412</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001810562823529412</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,26 +1026,26 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001810562823529412</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001810562823529412</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001810562823529412</v>
+        <v>0.001593295284705882</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
@@ -1083,7 +1082,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
@@ -1120,11 +1119,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.07694891999999998</v>
+        <v>0.2517556884201063</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,30 +1137,30 @@
         <v>1.292741856</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07694891999999998</v>
+        <v>0.08321550066999964</v>
       </c>
       <c r="G19" t="n">
         <v>1.292741856</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07694891999999039</v>
+        <v>0.083180565956307</v>
       </c>
       <c r="I19" t="n">
         <v>1.292741856</v>
       </c>
       <c r="J19" t="n">
-        <v>0.07694891999999998</v>
+        <v>0.238614690485051</v>
       </c>
       <c r="K19" t="n">
         <v>1.292741856</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.138330186832657</v>
+        <v>0.26932122</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,30 +1174,30 @@
         <v>1.292741856</v>
       </c>
       <c r="F20" t="n">
-        <v>0.138330186832657</v>
+        <v>0.08321550066999964</v>
       </c>
       <c r="G20" t="n">
         <v>1.292741856</v>
       </c>
       <c r="H20" t="n">
-        <v>0.138330186832657</v>
+        <v>0.083180565956307</v>
       </c>
       <c r="I20" t="n">
         <v>1.292741856</v>
       </c>
       <c r="J20" t="n">
-        <v>0.138330186832657</v>
+        <v>0.2488954845388334</v>
       </c>
       <c r="K20" t="n">
         <v>1.292741856</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.138330186832657</v>
+        <v>0.26932122</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,26 +1211,26 @@
         <v>1.292741856</v>
       </c>
       <c r="F21" t="n">
-        <v>0.138330186832657</v>
+        <v>0.08321550066999964</v>
       </c>
       <c r="G21" t="n">
         <v>1.292741856</v>
       </c>
       <c r="H21" t="n">
-        <v>0.138330186832657</v>
+        <v>0.083180565956307</v>
       </c>
       <c r="I21" t="n">
         <v>1.292741856</v>
       </c>
       <c r="J21" t="n">
-        <v>0.138330186832657</v>
+        <v>0.2488954845388334</v>
       </c>
       <c r="K21" t="n">
         <v>1.292741856</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1268,7 +1267,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1305,7 +1304,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1342,7 +1341,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1379,7 +1378,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1416,7 +1415,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
@@ -1453,7 +1452,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
@@ -1490,11 +1489,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.15389784</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,30 +1507,30 @@
         <v>1.292741856</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.3040759796687141</v>
       </c>
       <c r="G29" t="n">
         <v>1.292741856</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.3031277157904289</v>
       </c>
       <c r="I29" t="n">
         <v>1.292741856</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.1731919946040514</v>
       </c>
       <c r="K29" t="n">
         <v>1.292741856</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.15389784</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,30 +1544,30 @@
         <v>1.292741856</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.3040759796687141</v>
       </c>
       <c r="G30" t="n">
         <v>1.292741856</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.303127715790429</v>
       </c>
       <c r="I30" t="n">
         <v>1.292741856</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.1731919946040514</v>
       </c>
       <c r="K30" t="n">
         <v>1.292741856</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.15389784</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,26 +1581,26 @@
         <v>1.292741856</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.3040759796687141</v>
       </c>
       <c r="G31" t="n">
         <v>1.292741856</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.3036849858137597</v>
       </c>
       <c r="I31" t="n">
         <v>1.292741856</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.1731919946040514</v>
       </c>
       <c r="K31" t="n">
         <v>1.292741856</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1638,7 +1637,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1675,7 +1674,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1712,7 +1711,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1749,7 +1748,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1786,7 +1785,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1823,7 +1822,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1860,7 +1859,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1897,7 +1896,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1934,7 +1933,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1971,7 +1970,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -2008,7 +2007,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2045,7 +2044,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2082,7 +2081,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2119,7 +2118,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
@@ -2156,7 +2155,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2193,7 +2192,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
@@ -2230,7 +2229,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
@@ -2267,7 +2266,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
@@ -2304,7 +2303,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
@@ -2341,7 +2340,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
@@ -2378,7 +2377,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
@@ -2415,11 +2414,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>1.750069264647076</v>
+        <v>1.815520869612205</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,30 +2432,30 @@
         <v>6.213598185067377</v>
       </c>
       <c r="F54" t="n">
-        <v>1.679921096153434</v>
+        <v>1.683778479256591</v>
       </c>
       <c r="G54" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="H54" t="n">
-        <v>1.680713929272131</v>
+        <v>1.820210952414655</v>
       </c>
       <c r="I54" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="J54" t="n">
-        <v>1.744380854847067</v>
+        <v>1.68377847925659</v>
       </c>
       <c r="K54" t="n">
         <v>6.213598185067377</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>1.750069264647076</v>
+        <v>1.815520869612205</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,30 +2469,30 @@
         <v>6.213598185067377</v>
       </c>
       <c r="F55" t="n">
-        <v>1.679921096153434</v>
+        <v>1.683778479256591</v>
       </c>
       <c r="G55" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="H55" t="n">
-        <v>1.680713929272131</v>
+        <v>1.820210952414655</v>
       </c>
       <c r="I55" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="J55" t="n">
-        <v>1.744380854847067</v>
+        <v>1.68377847925659</v>
       </c>
       <c r="K55" t="n">
         <v>6.213598185067377</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>1.750069264647076</v>
+        <v>1.815520869612205</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,26 +2506,26 @@
         <v>6.213598185067377</v>
       </c>
       <c r="F56" t="n">
-        <v>1.679921096153434</v>
+        <v>1.683778479256591</v>
       </c>
       <c r="G56" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="H56" t="n">
-        <v>1.680713929272131</v>
+        <v>1.820210952414655</v>
       </c>
       <c r="I56" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="J56" t="n">
-        <v>1.744380854847067</v>
+        <v>1.68377847925659</v>
       </c>
       <c r="K56" t="n">
         <v>6.213598185067377</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2563,7 +2562,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2600,7 +2599,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2637,7 +2636,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2674,7 +2673,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2711,7 +2710,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2748,7 +2747,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
@@ -2785,11 +2784,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>1.014859152299939</v>
+        <v>0.4098816512464644</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,30 +2802,30 @@
         <v>6.213598185067377</v>
       </c>
       <c r="F64" t="n">
-        <v>1.095011366617428</v>
+        <v>0.5416240416020786</v>
       </c>
       <c r="G64" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="H64" t="n">
-        <v>1.08979663043032</v>
+        <v>0.4051915684440149</v>
       </c>
       <c r="I64" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="J64" t="n">
-        <v>1.026235971899957</v>
+        <v>0.5416240416020799</v>
       </c>
       <c r="K64" t="n">
         <v>6.213598185067377</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>1.014859152299939</v>
+        <v>0.4098816512464644</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,30 +2839,30 @@
         <v>6.213598185067377</v>
       </c>
       <c r="F65" t="n">
-        <v>1.095011366617428</v>
+        <v>0.5416240416020786</v>
       </c>
       <c r="G65" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="H65" t="n">
-        <v>1.08979663043032</v>
+        <v>0.4051915684440146</v>
       </c>
       <c r="I65" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="J65" t="n">
-        <v>1.026235971899957</v>
+        <v>0.5416240416020799</v>
       </c>
       <c r="K65" t="n">
         <v>6.213598185067377</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.787330759049493</v>
+        <v>0.9907228058198477</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,26 +2876,26 @@
         <v>6.213598185067377</v>
       </c>
       <c r="F66" t="n">
-        <v>1.878262647170586</v>
+        <v>1.122465196175461</v>
       </c>
       <c r="G66" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="H66" t="n">
-        <v>1.872109820536114</v>
+        <v>0.9860327230173971</v>
       </c>
       <c r="I66" t="n">
         <v>6.213598185067377</v>
       </c>
       <c r="J66" t="n">
-        <v>1.808442894961178</v>
+        <v>1.122465196175463</v>
       </c>
       <c r="K66" t="n">
         <v>6.213598185067377</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2933,7 +2932,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2970,7 +2969,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -3007,7 +3006,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3044,7 +3043,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3081,7 +3080,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3118,7 +3117,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3155,7 +3154,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3192,7 +3191,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3229,7 +3228,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3266,7 +3265,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
@@ -3303,7 +3302,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
@@ -3340,7 +3339,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
@@ -3377,7 +3376,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
@@ -3414,7 +3413,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
